--- a/Data/annees_scolaires.xlsx
+++ b/Data/annees_scolaires.xlsx
@@ -26,9 +26,6 @@
   </x:si>
   <x:si>
     <x:t>2025-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-2027</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -398,7 +395,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>3</x:v>
@@ -409,21 +406,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
